--- a/data/trans_orig/IP22D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3561</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6810</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3064</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5586</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5097</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7808</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7764</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9744</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4048</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9601</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10828</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11759</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>52,72%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>77,31%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5608</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>17471</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>53,07%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3451</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10911</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8934</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14281</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2974</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15210</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9602</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>62,54%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>8010</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5126</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>10362</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>67,84%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10755</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10755</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10755</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4091</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7566</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>33,12%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>61,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2628</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7813</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4522</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>83,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2471</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -2766,107 +2766,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12355</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5099</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14017</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>55,09%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>30398</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>63,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>32518</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>27179</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16782</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -3222,107 +3222,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
